--- a/output/CLARA MES 6_processado.xlsx
+++ b/output/CLARA MES 6_processado.xlsx
@@ -758,11 +758,7 @@
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1006,11 +1002,7 @@
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1130,11 +1122,7 @@
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1254,11 +1242,7 @@
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1378,11 +1362,7 @@
       <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1502,11 +1482,7 @@
       <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1626,11 +1602,7 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1750,11 +1722,7 @@
       <c r="AM10" t="inlineStr"/>
       <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1890,11 +1858,7 @@
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2014,11 +1978,7 @@
       <c r="AM12" t="inlineStr"/>
       <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2154,11 +2114,7 @@
       <c r="AM13" t="inlineStr"/>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2282,11 +2238,7 @@
       <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2406,11 +2358,7 @@
       <c r="AM15" t="inlineStr"/>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2530,11 +2478,7 @@
       <c r="AM16" t="inlineStr"/>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2654,11 +2598,7 @@
       <c r="AM17" t="inlineStr"/>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2778,11 +2718,7 @@
       <c r="AM18" t="inlineStr"/>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2902,11 +2838,7 @@
       <c r="AM19" t="inlineStr"/>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3026,11 +2958,7 @@
       <c r="AM20" t="inlineStr"/>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3150,11 +3078,7 @@
       <c r="AM21" t="inlineStr"/>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3522,11 +3446,7 @@
       <c r="AM24" t="inlineStr"/>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3770,11 +3690,7 @@
       <c r="AM26" t="inlineStr"/>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3894,11 +3810,7 @@
       <c r="AM27" t="inlineStr"/>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4018,11 +3930,7 @@
       <c r="AM28" t="inlineStr"/>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4142,11 +4050,7 @@
       <c r="AM29" t="inlineStr"/>
       <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4266,11 +4170,7 @@
       <c r="AM30" t="inlineStr"/>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4390,11 +4290,7 @@
       <c r="AM31" t="inlineStr"/>
       <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4638,11 +4534,7 @@
       <c r="AM33" t="inlineStr"/>
       <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4762,11 +4654,7 @@
       <c r="AM34" t="inlineStr"/>
       <c r="AN34" t="inlineStr"/>
       <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4886,11 +4774,7 @@
       <c r="AM35" t="inlineStr"/>
       <c r="AN35" t="inlineStr"/>
       <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5010,11 +4894,7 @@
       <c r="AM36" t="inlineStr"/>
       <c r="AN36" t="inlineStr"/>
       <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5134,11 +5014,7 @@
       <c r="AM37" t="inlineStr"/>
       <c r="AN37" t="inlineStr"/>
       <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5258,11 +5134,7 @@
       <c r="AM38" t="inlineStr"/>
       <c r="AN38" t="inlineStr"/>
       <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5382,11 +5254,7 @@
       <c r="AM39" t="inlineStr"/>
       <c r="AN39" t="inlineStr"/>
       <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5506,11 +5374,7 @@
       <c r="AM40" t="inlineStr"/>
       <c r="AN40" t="inlineStr"/>
       <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5630,11 +5494,7 @@
       <c r="AM41" t="inlineStr"/>
       <c r="AN41" t="inlineStr"/>
       <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5754,11 +5614,7 @@
       <c r="AM42" t="inlineStr"/>
       <c r="AN42" t="inlineStr"/>
       <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5878,11 +5734,7 @@
       <c r="AM43" t="inlineStr"/>
       <c r="AN43" t="inlineStr"/>
       <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6002,11 +5854,7 @@
       <c r="AM44" t="inlineStr"/>
       <c r="AN44" t="inlineStr"/>
       <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6126,11 +5974,7 @@
       <c r="AM45" t="inlineStr"/>
       <c r="AN45" t="inlineStr"/>
       <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6266,11 +6110,7 @@
       <c r="AM46" t="inlineStr"/>
       <c r="AN46" t="inlineStr"/>
       <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6406,11 +6246,7 @@
       <c r="AM47" t="inlineStr"/>
       <c r="AN47" t="inlineStr"/>
       <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6546,11 +6382,7 @@
       <c r="AM48" t="inlineStr"/>
       <c r="AN48" t="inlineStr"/>
       <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6670,11 +6502,7 @@
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6810,11 +6638,7 @@
       <c r="AM50" t="inlineStr"/>
       <c r="AN50" t="inlineStr"/>
       <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>PENDENTE | Tipo não-LATAM ainda não implementado neste fluxo</t>
-        </is>
-      </c>
+      <c r="AP50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/CLARA MES 6_processado.xlsx
+++ b/output/CLARA MES 6_processado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,7 +880,7 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>ERRO | localizador SQOZBP não encontrado nos títulos disponíveis</t>
+          <t>OK Vendas | Venda 00031289 | Loc SQOZBP</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>ERRO | localizador HNJAXE não encontrado nos títulos disponíveis</t>
+          <t>ERRO | Venda 00031062: TargetClosedError: Page.wait_for_timeout: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>ERRO | localizador GXMNCV não encontrado nos títulos disponíveis</t>
+          <t>ERRO | Busca Vendas: TargetClosedError: Locator.count: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>ERRO | localizador WGUQJO não encontrado nos títulos disponíveis</t>
+          <t>ERRO | Busca Vendas: TargetClosedError: Locator.count: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>ERRO | localizador WIPOEV não encontrado nos títulos disponíveis</t>
+          <t>ERRO | Busca Vendas: TargetClosedError: Locator.count: Target page, context or browser has been closed</t>
         </is>
       </c>
     </row>
